--- a/public/downloads/shopfloor-matters-swimlane-process-map.xlsx
+++ b/public/downloads/shopfloor-matters-swimlane-process-map.xlsx
@@ -417,80 +417,84 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -750,130 +754,130 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -906,222 +910,222 @@
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="1" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="12" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="13"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="12" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="12" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="12" t="s">
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="12" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="12" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="12" t="s">
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="13"/>
+      <c r="K11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14" t="s">
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14" t="s">
+      <c r="H12" s="14"/>
+      <c r="I12" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1148,183 +1152,183 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="1" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1349,505 +1353,505 @@
   <dimension ref="A1:I33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="17" t="n">
         <f aca="false">IF(AND(ISNUMBER(E5),ISNUMBER(F5)),E5*F5*48/60,"")</f>
         <v>240</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="16" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="16" t="str">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E6),ISNUMBER(F6)),E6*F6*48/60,"")</f>
         <v/>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="16" t="str">
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E7),ISNUMBER(F7)),E7*F7*48/60,"")</f>
         <v/>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16" t="str">
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E8),ISNUMBER(F8)),E8*F8*48/60,"")</f>
         <v/>
       </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16" t="str">
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E9),ISNUMBER(F9)),E9*F9*48/60,"")</f>
         <v/>
       </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16" t="str">
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E10),ISNUMBER(F10)),E10*F10*48/60,"")</f>
         <v/>
       </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16" t="str">
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E11),ISNUMBER(F11)),E11*F11*48/60,"")</f>
         <v/>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16" t="str">
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E12),ISNUMBER(F12)),E12*F12*48/60,"")</f>
         <v/>
       </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16" t="str">
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E13),ISNUMBER(F13)),E13*F13*48/60,"")</f>
         <v/>
       </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="16" t="str">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E14),ISNUMBER(F14)),E14*F14*48/60,"")</f>
         <v/>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16" t="str">
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E15),ISNUMBER(F15)),E15*F15*48/60,"")</f>
         <v/>
       </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16" t="str">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E16),ISNUMBER(F16)),E16*F16*48/60,"")</f>
         <v/>
       </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16" t="str">
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E17),ISNUMBER(F17)),E17*F17*48/60,"")</f>
         <v/>
       </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16" t="str">
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E18),ISNUMBER(F18)),E18*F18*48/60,"")</f>
         <v/>
       </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16" t="str">
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E19),ISNUMBER(F19)),E19*F19*48/60,"")</f>
         <v/>
       </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16" t="str">
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E20),ISNUMBER(F20)),E20*F20*48/60,"")</f>
         <v/>
       </c>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16" t="str">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E21),ISNUMBER(F21)),E21*F21*48/60,"")</f>
         <v/>
       </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16" t="str">
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E22),ISNUMBER(F22)),E22*F22*48/60,"")</f>
         <v/>
       </c>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="16" t="str">
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E23),ISNUMBER(F23)),E23*F23*48/60,"")</f>
         <v/>
       </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="16" t="str">
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E24),ISNUMBER(F24)),E24*F24*48/60,"")</f>
         <v/>
       </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="16" t="str">
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E25),ISNUMBER(F25)),E25*F25*48/60,"")</f>
         <v/>
       </c>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="16" t="str">
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E26),ISNUMBER(F26)),E26*F26*48/60,"")</f>
         <v/>
       </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16" t="str">
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E27),ISNUMBER(F27)),E27*F27*48/60,"")</f>
         <v/>
       </c>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16" t="str">
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E28),ISNUMBER(F28)),E28*F28*48/60,"")</f>
         <v/>
       </c>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="16" t="str">
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E29),ISNUMBER(F29)),E29*F29*48/60,"")</f>
         <v/>
       </c>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="16" t="str">
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17" t="str">
         <f aca="false">IF(AND(ISNUMBER(E30),ISNUMBER(F30)),E30*F30*48/60,"")</f>
         <v/>
       </c>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="G32" s="18" t="n">
+      <c r="G32" s="19" t="n">
         <f aca="false">SUM(G5:G30)</f>
         <v>240</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="9" t="s">
         <v>73</v>
       </c>
     </row>

--- a/public/downloads/shopfloor-matters-swimlane-process-map.xlsx
+++ b/public/downloads/shopfloor-matters-swimlane-process-map.xlsx
@@ -417,84 +417,80 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -754,130 +750,130 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -910,222 +906,222 @@
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="13" t="s">
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="14"/>
+      <c r="K5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="13" t="s">
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="13" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="13" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="13" t="s">
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="13" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="13" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="13" t="s">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="14"/>
+      <c r="K11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15" t="s">
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="15" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="s">
+      <c r="H12" s="13"/>
+      <c r="I12" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1152,183 +1148,183 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1353,505 +1349,505 @@
   <dimension ref="A1:I33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="16" t="n">
         <f aca="false">IF(AND(ISNUMBER(E5),ISNUMBER(F5)),E5*F5*48/60,"")</f>
         <v>240</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="15" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17" t="str">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E6),ISNUMBER(F6)),E6*F6*48/60,"")</f>
         <v/>
       </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="17" t="str">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E7),ISNUMBER(F7)),E7*F7*48/60,"")</f>
         <v/>
       </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17" t="str">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E8),ISNUMBER(F8)),E8*F8*48/60,"")</f>
         <v/>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17" t="str">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E9),ISNUMBER(F9)),E9*F9*48/60,"")</f>
         <v/>
       </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17" t="str">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E10),ISNUMBER(F10)),E10*F10*48/60,"")</f>
         <v/>
       </c>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17" t="str">
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E11),ISNUMBER(F11)),E11*F11*48/60,"")</f>
         <v/>
       </c>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17" t="str">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E12),ISNUMBER(F12)),E12*F12*48/60,"")</f>
         <v/>
       </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17" t="str">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E13),ISNUMBER(F13)),E13*F13*48/60,"")</f>
         <v/>
       </c>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17" t="str">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E14),ISNUMBER(F14)),E14*F14*48/60,"")</f>
         <v/>
       </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17" t="str">
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E15),ISNUMBER(F15)),E15*F15*48/60,"")</f>
         <v/>
       </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="17" t="str">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E16),ISNUMBER(F16)),E16*F16*48/60,"")</f>
         <v/>
       </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17" t="str">
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E17),ISNUMBER(F17)),E17*F17*48/60,"")</f>
         <v/>
       </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17" t="str">
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E18),ISNUMBER(F18)),E18*F18*48/60,"")</f>
         <v/>
       </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="17" t="str">
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E19),ISNUMBER(F19)),E19*F19*48/60,"")</f>
         <v/>
       </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="17" t="str">
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E20),ISNUMBER(F20)),E20*F20*48/60,"")</f>
         <v/>
       </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="17" t="str">
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E21),ISNUMBER(F21)),E21*F21*48/60,"")</f>
         <v/>
       </c>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="17" t="str">
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E22),ISNUMBER(F22)),E22*F22*48/60,"")</f>
         <v/>
       </c>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="17" t="str">
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E23),ISNUMBER(F23)),E23*F23*48/60,"")</f>
         <v/>
       </c>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="17" t="str">
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E24),ISNUMBER(F24)),E24*F24*48/60,"")</f>
         <v/>
       </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17" t="str">
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E25),ISNUMBER(F25)),E25*F25*48/60,"")</f>
         <v/>
       </c>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17" t="str">
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E26),ISNUMBER(F26)),E26*F26*48/60,"")</f>
         <v/>
       </c>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="17" t="str">
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E27),ISNUMBER(F27)),E27*F27*48/60,"")</f>
         <v/>
       </c>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="17" t="str">
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E28),ISNUMBER(F28)),E28*F28*48/60,"")</f>
         <v/>
       </c>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="17" t="str">
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E29),ISNUMBER(F29)),E29*F29*48/60,"")</f>
         <v/>
       </c>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="17" t="str">
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16" t="str">
         <f aca="false">IF(AND(ISNUMBER(E30),ISNUMBER(F30)),E30*F30*48/60,"")</f>
         <v/>
       </c>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="G32" s="19" t="n">
+      <c r="G32" s="18" t="n">
         <f aca="false">SUM(G5:G30)</f>
         <v>240</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="8" t="s">
         <v>73</v>
       </c>
     </row>
